--- a/output/pdf_financials_xlsx/PKT.xlsx
+++ b/output/pdf_financials_xlsx/PKT.xlsx
@@ -6409,31 +6409,31 @@
         <v>3.07136</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>4.258043</v>
+        <v>0.811306</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.7062850000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.614712</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.293707</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.214397</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.367154</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.467005</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.472381</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.027094</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>3.175065</v>
@@ -7050,10 +7050,10 @@
         <v>-0.013852</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.007732</v>
+        <v>0.000489</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.053362</v>
       </c>
       <c r="F103" s="3" t="n">
         <v>0.030212</v>
@@ -7233,10 +7233,10 @@
         <v>-0.035338</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.12114</v>
+        <v>0.113897</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.783536</v>
+        <v>0.730174</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-3.469949</v>
@@ -13362,7 +13362,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -16012,7 +16016,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -18042,7 +18050,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -20250,7 +20262,11 @@
           <t>Reserves (Note 16)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -22460,7 +22476,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -47084,7 +47104,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PKT.xlsx
+++ b/output/pdf_financials_xlsx/PKT.xlsx
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004545</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2162,7 +2162,7 @@
         <v>-6.368494</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.489558</v>
+        <v>-7.494103</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-3.589264</v>
@@ -2284,7 +2284,7 @@
         <v>-6.367245</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.464815</v>
+        <v>-6.46936</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.458144</v>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-201.8934178363964</v>
+        <v>-202.0353562498029</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-38.90071561729509</v>
@@ -2576,28 +2576,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.358827</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.689523</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.167217</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.637517</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.041286</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.268884</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.563515</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.237061</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.55216</v>
@@ -2612,19 +2612,19 @@
         <v>0.768434</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>21.797256</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>19.471763</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>10.556555</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>5.476859</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>5.38229</v>
       </c>
     </row>
     <row r="35">
@@ -2702,28 +2702,28 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.358827</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.689523</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.167217</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.637517</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.041286</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.268884</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.563515</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.237061</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1.55216</v>
@@ -2738,19 +2738,19 @@
         <v>0.768434</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>21.797256</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>19.471763</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>10.556555</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>5.476859</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>5.38229</v>
       </c>
     </row>
     <row r="37">
@@ -3458,28 +3458,28 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.455375</v>
+        <v>0.09654799999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.871883</v>
+        <v>0.18236</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.09656</v>
+        <v>1.929343</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.751098</v>
+        <v>1.113581</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.45651</v>
+        <v>1.415224</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.389343</v>
+        <v>2.120459</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.09796</v>
+        <v>0.5344449999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.259998</v>
+        <v>0.022937</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.023895</v>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -74160,7 +74160,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
